--- a/log/测试用例_yjyx.xlsx
+++ b/log/测试用例_yjyx.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\tools\projects\auto_yjyj\log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B687B506-D50F-4BC9-8AA6-59554D78D844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B18D55-0A5A-4A87-8D97-D5083780A939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="登录登出" sheetId="1" r:id="rId1"/>
     <sheet name="首页信息" sheetId="2" r:id="rId2"/>
     <sheet name="题目管理" sheetId="3" r:id="rId3"/>
     <sheet name="作业功能" sheetId="4" r:id="rId4"/>
-    <sheet name="api" sheetId="5" r:id="rId5"/>
+    <sheet name="手机App" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">登录登出!$A$1:$I$16</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1888" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="985">
   <si>
     <t>类别</t>
   </si>
@@ -1440,9 +1440,6 @@
   </si>
   <si>
     <t>TC_HOMEWORK_005</t>
-  </si>
-  <si>
-    <t>TC_HOMEWORK_006</t>
   </si>
   <si>
     <t>TC_HOMEWORK_007</t>
@@ -5652,12 +5649,289 @@
 2.设置任务描述为20个字符串，确定下发</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
+  <si>
+    <t>vcode登录1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 提示      登录失败 : vcode format error:1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>vcode登录2</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 登录成功，进入到app班级管理页，并且显示 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该学校还没有班级，点击刷新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+进入到老师管理页，显示 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该学校还没有老师，点击刷新</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>vcode登录3</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 登录成功，进入到app 
+班级管理页，并且显示 班级的信息正确
+进入到老师管理页，并且显示 老师的信息正确</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加班级1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 进入到添加班级的界面
+2. 显示  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">添加成功的 提示
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+班级界面中正确多出了刚刚添加的班级信息
+使用 亿教 WEB API 调用列出班级的信息，多出了刚刚添加的班级的信息</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>添加老师1</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 进入到添加老师的界面
+2. APP 显示  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">添加成功的 提示
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+APP 老师界面中正确多出了刚刚添加的老师信息
+3. 登录成功，进入老师首页，其中 学校、姓名、学科、金币、已发布微课、已发布作业 的信息正确
+4. 显示学生列表为空</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 使用无效的vcode登录
+</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 使用有效的vcode登录
+</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 进入app班级管理界面，点击添加一个班级
+2. 输入正确的班级信息，点击添加
+</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 进入app老师管理界面，点击添加一个老师
+2. 输入正确的老师信息，点击添加
+3. 以创建老师的账号和密码（初始密码为888888）登录 web系统
+4. 点击 班级学生 菜单
+</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还没有老师，没有班级，没有学生，还没有使用vcode登录</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有1名老师，1个班级，没有学生，还没有使用vcode登录</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还没有老师，没有班级，app已经使用vcode登录</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系统中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>还没有老师，已经有班级，没有学生，app已经使用vcode登录</t>
+    </r>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC_HOMEWORK_006</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC_APP_6001</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC_APP_6002</t>
+  </si>
+  <si>
+    <t>TC_APP_6003</t>
+  </si>
+  <si>
+    <t>TC_APP_6101</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>TC_APP_6201</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5742,9 +6016,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF00BF00"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -5752,11 +6025,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00BF00"/>
-      <name val="宋体"/>
-      <family val="3"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="8">
@@ -5817,7 +6095,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5892,9 +6170,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -5908,19 +6183,19 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5938,7 +6213,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -5946,6 +6221,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6294,25 +6581,25 @@
         <v>33</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>453</v>
+      <c r="E4" s="26" t="s">
+        <v>452</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="I4" s="36" t="s">
-        <v>953</v>
+        <v>451</v>
+      </c>
+      <c r="I4" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="141.65" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6324,10 +6611,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>945</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>467</v>
+        <v>944</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>466</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>14</v>
@@ -6338,8 +6625,8 @@
       <c r="H5" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="36" t="s">
-        <v>953</v>
+      <c r="I5" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="89.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6353,20 +6640,20 @@
       <c r="D6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>946</v>
+      <c r="E6" s="26" t="s">
+        <v>945</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H6" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="I6" s="36" t="s">
-        <v>953</v>
+      <c r="I6" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="108" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6380,7 +6667,7 @@
       <c r="D7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -6392,8 +6679,8 @@
       <c r="H7" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="36" t="s">
-        <v>953</v>
+      <c r="I7" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6407,11 +6694,11 @@
       <c r="D8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="27" t="s">
-        <v>955</v>
+      <c r="E8" s="26" t="s">
+        <v>954</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>45</v>
@@ -6419,14 +6706,14 @@
       <c r="H8" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I8" s="37" t="s">
-        <v>956</v>
+      <c r="I8" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>37</v>
@@ -6434,11 +6721,11 @@
       <c r="D9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="27" t="s">
-        <v>954</v>
+      <c r="E9" s="26" t="s">
+        <v>953</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>40</v>
@@ -6446,35 +6733,35 @@
       <c r="H9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="37" t="s">
-        <v>956</v>
+      <c r="I9" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>39</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>477</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>956</v>
+      <c r="I10" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6488,11 +6775,11 @@
       <c r="D11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>44</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G11" s="9" t="s">
         <v>28</v>
@@ -6500,8 +6787,8 @@
       <c r="H11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="36" t="s">
-        <v>953</v>
+      <c r="I11" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6515,11 +6802,11 @@
       <c r="D12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>49</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>32</v>
@@ -6527,8 +6814,8 @@
       <c r="H12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>953</v>
+      <c r="I12" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="25" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6537,25 +6824,25 @@
         <v>33</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>54</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="36" t="s">
-        <v>953</v>
+      <c r="I13" s="35" t="s">
+        <v>952</v>
       </c>
       <c r="K13" s="11"/>
       <c r="N13" s="11"/>
@@ -6574,8 +6861,8 @@
       <c r="D14" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>486</v>
+      <c r="E14" s="26" t="s">
+        <v>485</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>22</v>
@@ -6586,8 +6873,8 @@
       <c r="H14" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="36" t="s">
-        <v>953</v>
+      <c r="I14" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="56.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6599,22 +6886,22 @@
         <v>52</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>464</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>64</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="I15" s="37" t="s">
-        <v>956</v>
+      <c r="I15" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="56.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6626,10 +6913,10 @@
         <v>57</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>481</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>487</v>
+        <v>480</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>486</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>22</v>
@@ -6640,8 +6927,8 @@
       <c r="H16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="37" t="s">
-        <v>956</v>
+      <c r="I16" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6653,7 +6940,7 @@
       <c r="F17" s="9"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="38"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
@@ -6666,7 +6953,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
-      <c r="I18" s="39"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
@@ -6679,8 +6966,8 @@
       <c r="D19" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="27" t="s">
-        <v>454</v>
+      <c r="E19" s="26" t="s">
+        <v>453</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>22</v>
@@ -6691,8 +6978,8 @@
       <c r="H19" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I19" s="36" t="s">
-        <v>953</v>
+      <c r="I19" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -6706,20 +6993,20 @@
       <c r="D20" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="27" t="s">
-        <v>490</v>
+      <c r="E20" s="26" t="s">
+        <v>489</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H20" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="36" t="s">
-        <v>953</v>
+      <c r="I20" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -6731,7 +7018,7 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="38"/>
+      <c r="I21" s="37"/>
     </row>
     <row r="22" spans="1:9" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
@@ -6744,7 +7031,7 @@
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="40"/>
+      <c r="I22" s="39"/>
     </row>
     <row r="23" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
@@ -6757,7 +7044,7 @@
       <c r="F23" s="16"/>
       <c r="G23" s="16"/>
       <c r="H23" s="16"/>
-      <c r="I23" s="41"/>
+      <c r="I23" s="40"/>
     </row>
     <row r="24" spans="1:9" ht="56.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
@@ -6765,25 +7052,25 @@
         <v>11</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>455</v>
+      <c r="E24" s="26" t="s">
+        <v>454</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>953</v>
+        <v>450</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="108.65" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6797,20 +7084,20 @@
       <c r="D25" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="E25" s="27" t="s">
-        <v>456</v>
+      <c r="E25" s="26" t="s">
+        <v>455</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H25" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="I25" s="42" t="s">
-        <v>953</v>
+      <c r="I25" s="41" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="99.65" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6824,11 +7111,11 @@
       <c r="D26" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="E26" s="27" t="s">
-        <v>457</v>
+      <c r="E26" s="26" t="s">
+        <v>456</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G26" s="9" t="s">
         <v>78</v>
@@ -6836,8 +7123,8 @@
       <c r="H26" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="I26" s="36" t="s">
-        <v>953</v>
+      <c r="I26" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6851,8 +7138,8 @@
       <c r="D27" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="27" t="s">
-        <v>943</v>
+      <c r="E27" s="26" t="s">
+        <v>942</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>81</v>
@@ -6863,8 +7150,8 @@
       <c r="H27" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="36" t="s">
-        <v>953</v>
+      <c r="I27" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6878,8 +7165,8 @@
       <c r="D28" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E28" s="27" t="s">
-        <v>942</v>
+      <c r="E28" s="26" t="s">
+        <v>941</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>81</v>
@@ -6890,8 +7177,8 @@
       <c r="H28" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="I28" s="37" t="s">
-        <v>956</v>
+      <c r="I28" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6900,13 +7187,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="27" t="s">
-        <v>458</v>
+      <c r="E29" s="26" t="s">
+        <v>457</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>81</v>
@@ -6917,8 +7204,8 @@
       <c r="H29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="I29" s="37" t="s">
-        <v>956</v>
+      <c r="I29" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6932,8 +7219,8 @@
       <c r="D30" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="27" t="s">
-        <v>459</v>
+      <c r="E30" s="26" t="s">
+        <v>458</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>81</v>
@@ -6942,10 +7229,10 @@
         <v>87</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>941</v>
-      </c>
-      <c r="I30" s="37" t="s">
-        <v>956</v>
+        <v>940</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6959,20 +7246,20 @@
       <c r="D31" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="E31" s="27" t="s">
-        <v>460</v>
+      <c r="E31" s="26" t="s">
+        <v>459</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>81</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I31" s="36" t="s">
-        <v>953</v>
+      <c r="I31" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -6986,8 +7273,8 @@
       <c r="D32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E32" s="27" t="s">
-        <v>461</v>
+      <c r="E32" s="26" t="s">
+        <v>460</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>81</v>
@@ -6998,8 +7285,8 @@
       <c r="H32" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I32" s="36" t="s">
-        <v>953</v>
+      <c r="I32" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -7008,25 +7295,25 @@
         <v>11</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E33" s="27" t="s">
-        <v>462</v>
+      <c r="E33" s="26" t="s">
+        <v>461</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>81</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I33" s="36" t="s">
-        <v>953</v>
+      <c r="I33" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -7040,8 +7327,8 @@
       <c r="D34" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="E34" s="27" t="s">
-        <v>951</v>
+      <c r="E34" s="26" t="s">
+        <v>950</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>93</v>
@@ -7052,8 +7339,8 @@
       <c r="H34" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I34" s="36" t="s">
-        <v>953</v>
+      <c r="I34" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="86.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -7065,22 +7352,22 @@
         <v>52</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>948</v>
+        <v>465</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>947</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>81</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="I35" s="37" t="s">
-        <v>956</v>
+      <c r="I35" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -7089,13 +7376,13 @@
         <v>56</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>949</v>
+        <v>474</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>948</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>22</v>
@@ -7104,10 +7391,10 @@
         <v>98</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>950</v>
-      </c>
-      <c r="I36" s="36" t="s">
-        <v>953</v>
+        <v>949</v>
+      </c>
+      <c r="I36" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="37" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7119,7 +7406,7 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
-      <c r="I37" s="43"/>
+      <c r="I37" s="42"/>
     </row>
     <row r="38" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
@@ -7132,7 +7419,7 @@
       <c r="F38" s="16"/>
       <c r="G38" s="16"/>
       <c r="H38" s="16"/>
-      <c r="I38" s="41"/>
+      <c r="I38" s="40"/>
     </row>
     <row r="39" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
@@ -7144,20 +7431,20 @@
       <c r="D39" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="E39" s="27" t="s">
-        <v>463</v>
+      <c r="E39" s="26" t="s">
+        <v>462</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>81</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>488</v>
-      </c>
-      <c r="I39" s="36" t="s">
-        <v>953</v>
+        <v>487</v>
+      </c>
+      <c r="I39" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -7170,8 +7457,8 @@
       <c r="D40" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E40" s="27" t="s">
-        <v>464</v>
+      <c r="E40" s="26" t="s">
+        <v>463</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>81</v>
@@ -7182,8 +7469,8 @@
       <c r="H40" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="I40" s="36" t="s">
-        <v>953</v>
+      <c r="I40" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -7261,8 +7548,8 @@
       <c r="D3" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="27" t="s">
-        <v>516</v>
+      <c r="E3" s="26" t="s">
+        <v>515</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>106</v>
@@ -7273,8 +7560,8 @@
       <c r="H3" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="I3" s="36" t="s">
-        <v>953</v>
+      <c r="I3" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="88.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7285,10 +7572,10 @@
         <v>109</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>491</v>
+        <v>503</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>490</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>112</v>
@@ -7299,8 +7586,8 @@
       <c r="H4" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I4" s="37" t="s">
-        <v>956</v>
+      <c r="I4" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="88.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7313,20 +7600,20 @@
       <c r="D5" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>111</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="36" t="s">
-        <v>953</v>
+      <c r="I5" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="88.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7339,8 +7626,8 @@
       <c r="D6" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>947</v>
+      <c r="E6" s="26" t="s">
+        <v>946</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>22</v>
@@ -7351,8 +7638,8 @@
       <c r="H6" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I6" s="36" t="s">
-        <v>953</v>
+      <c r="I6" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7365,7 +7652,7 @@
       <c r="D7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>120</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -7377,8 +7664,8 @@
       <c r="H7" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="36" t="s">
-        <v>953</v>
+      <c r="I7" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7391,7 +7678,7 @@
       <c r="D8" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>125</v>
       </c>
       <c r="F8" s="9" t="s">
@@ -7403,8 +7690,8 @@
       <c r="H8" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I8" s="36" t="s">
-        <v>953</v>
+      <c r="I8" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="80.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7418,7 +7705,7 @@
       <c r="D9" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>129</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -7430,8 +7717,8 @@
       <c r="H9" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="I9" s="36" t="s">
-        <v>953</v>
+      <c r="I9" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="80.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7445,20 +7732,20 @@
       <c r="D10" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>132</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>506</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>956</v>
+      <c r="I10" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="80.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7472,20 +7759,20 @@
       <c r="D11" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="E11" s="27" t="s">
-        <v>513</v>
+      <c r="E11" s="26" t="s">
+        <v>512</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G11" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="H11" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="I11" s="36" t="s">
-        <v>953</v>
+      <c r="I11" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="80.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7497,10 +7784,10 @@
         <v>135</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>514</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>511</v>
+        <v>513</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>510</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>22</v>
@@ -7511,8 +7798,8 @@
       <c r="H12" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="I12" s="36" t="s">
-        <v>953</v>
+      <c r="I12" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="119.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7524,10 +7811,10 @@
         <v>139</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>515</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>512</v>
+        <v>514</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>511</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>22</v>
@@ -7536,10 +7823,10 @@
         <v>140</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="I13" s="36" t="s">
-        <v>953</v>
+        <v>509</v>
+      </c>
+      <c r="I13" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="58" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -7551,7 +7838,7 @@
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="38"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:9" customFormat="1" ht="28" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
@@ -7564,7 +7851,7 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-      <c r="I15" s="44"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="1:9" customFormat="1" ht="60.65" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
@@ -7577,8 +7864,8 @@
       <c r="D16" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="E16" s="27" t="s">
-        <v>492</v>
+      <c r="E16" s="26" t="s">
+        <v>491</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>144</v>
@@ -7587,10 +7874,10 @@
         <v>145</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="I16" s="36" t="s">
-        <v>953</v>
+        <v>502</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7604,8 +7891,8 @@
       <c r="D17" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>493</v>
+      <c r="E17" s="26" t="s">
+        <v>492</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>148</v>
@@ -7616,8 +7903,8 @@
       <c r="H17" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="36" t="s">
-        <v>953</v>
+      <c r="I17" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="43" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7631,8 +7918,8 @@
       <c r="D18" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="27" t="s">
-        <v>494</v>
+      <c r="E18" s="26" t="s">
+        <v>493</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>150</v>
@@ -7643,8 +7930,8 @@
       <c r="H18" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="36" t="s">
-        <v>953</v>
+      <c r="I18" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7658,8 +7945,8 @@
       <c r="D19" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="27" t="s">
-        <v>495</v>
+      <c r="E19" s="26" t="s">
+        <v>494</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>93</v>
@@ -7670,8 +7957,8 @@
       <c r="H19" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I19" s="36" t="s">
-        <v>953</v>
+      <c r="I19" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7685,8 +7972,8 @@
       <c r="D20" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E20" s="27" t="s">
-        <v>496</v>
+      <c r="E20" s="26" t="s">
+        <v>495</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>93</v>
@@ -7697,8 +7984,8 @@
       <c r="H20" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I20" s="36" t="s">
-        <v>953</v>
+      <c r="I20" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="84" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7712,8 +7999,8 @@
       <c r="D21" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E21" s="27" t="s">
-        <v>497</v>
+      <c r="E21" s="26" t="s">
+        <v>496</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>93</v>
@@ -7724,8 +8011,8 @@
       <c r="H21" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="I21" s="36" t="s">
-        <v>953</v>
+      <c r="I21" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="70" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7739,8 +8026,8 @@
       <c r="D22" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="E22" s="27" t="s">
-        <v>498</v>
+      <c r="E22" s="26" t="s">
+        <v>497</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>93</v>
@@ -7751,8 +8038,8 @@
       <c r="H22" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="I22" s="37" t="s">
-        <v>956</v>
+      <c r="I22" s="36" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7766,20 +8053,20 @@
       <c r="D23" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="E23" s="27" t="s">
-        <v>499</v>
+      <c r="E23" s="26" t="s">
+        <v>498</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>93</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>507</v>
-      </c>
-      <c r="I23" s="36" t="s">
-        <v>953</v>
+        <v>506</v>
+      </c>
+      <c r="I23" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7793,20 +8080,20 @@
       <c r="D24" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="27" t="s">
-        <v>500</v>
+      <c r="E24" s="26" t="s">
+        <v>499</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>93</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>509</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>953</v>
+        <v>508</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7820,11 +8107,11 @@
       <c r="D25" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="E25" s="27" t="s">
-        <v>501</v>
+      <c r="E25" s="26" t="s">
+        <v>500</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>169</v>
@@ -7832,8 +8119,8 @@
       <c r="H25" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="I25" s="36" t="s">
-        <v>953</v>
+      <c r="I25" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7847,8 +8134,8 @@
       <c r="D26" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="E26" s="27" t="s">
-        <v>502</v>
+      <c r="E26" s="26" t="s">
+        <v>501</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>93</v>
@@ -7857,10 +8144,10 @@
         <v>171</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>510</v>
-      </c>
-      <c r="I26" s="36" t="s">
-        <v>953</v>
+        <v>509</v>
+      </c>
+      <c r="I26" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7872,10 +8159,10 @@
         <v>160</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>517</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>522</v>
+        <v>516</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>521</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>162</v>
@@ -7886,8 +8173,8 @@
       <c r="H27" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="I27" s="36" t="s">
-        <v>953</v>
+      <c r="I27" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -7899,10 +8186,10 @@
         <v>160</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>518</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>523</v>
+        <v>517</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>522</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>162</v>
@@ -7913,8 +8200,8 @@
       <c r="H28" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="I28" s="36" t="s">
-        <v>953</v>
+      <c r="I28" s="35" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8006,7 +8293,7 @@
     </row>
     <row r="2" spans="1:9" s="8" customFormat="1" ht="17.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -8026,22 +8313,22 @@
         <v>172</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>526</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>524</v>
+        <v>525</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>523</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H3" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I3" s="32" t="s">
-        <v>953</v>
+      <c r="I3" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="8" customFormat="1" ht="171" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8053,22 +8340,22 @@
         <v>172</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>527</v>
-      </c>
-      <c r="E4" s="27" t="s">
+        <v>526</v>
+      </c>
+      <c r="E4" s="26" t="s">
         <v>175</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H4" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I4" s="32" t="s">
-        <v>953</v>
+      <c r="I4" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="8" customFormat="1" ht="178" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8080,22 +8367,22 @@
         <v>176</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>528</v>
-      </c>
-      <c r="E5" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="E5" s="26" t="s">
         <v>177</v>
       </c>
       <c r="F5" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="I5" s="32" t="s">
-        <v>953</v>
+        <v>568</v>
+      </c>
+      <c r="I5" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="8" customFormat="1" ht="67.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8107,22 +8394,22 @@
         <v>178</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>529</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>957</v>
+        <v>528</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>956</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>953</v>
+        <v>569</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="8" customFormat="1" ht="67.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8134,22 +8421,22 @@
         <v>178</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>530</v>
-      </c>
-      <c r="E7" s="27" t="s">
+        <v>529</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>180</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>956</v>
+      <c r="I7" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="8" customFormat="1" ht="74.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8161,22 +8448,22 @@
         <v>178</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E8" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="E8" s="26" t="s">
         <v>181</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I8" s="35" t="s">
-        <v>956</v>
+      <c r="I8" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="8" customFormat="1" ht="74.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8188,9 +8475,9 @@
         <v>183</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="E9" s="27" t="s">
+        <v>531</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>184</v>
       </c>
       <c r="F9" s="9" t="s">
@@ -8200,10 +8487,10 @@
         <v>185</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>953</v>
+        <v>570</v>
+      </c>
+      <c r="I9" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="8" customFormat="1" ht="86.15" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8215,22 +8502,22 @@
         <v>186</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="E10" s="27" t="s">
+        <v>532</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>187</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G10" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="I10" s="35" t="s">
-        <v>956</v>
+      <c r="I10" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="8" customFormat="1" ht="212.15" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8242,7 +8529,7 @@
         <v>188</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>189</v>
@@ -8251,7 +8538,7 @@
         <v>173</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>190</v>
@@ -8266,7 +8553,7 @@
         <v>188</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>191</v>
@@ -8290,22 +8577,22 @@
         <v>194</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>536</v>
-      </c>
-      <c r="E13" s="27" t="s">
+        <v>535</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>953</v>
+      <c r="I13" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="8" customFormat="1" ht="111" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8317,22 +8604,22 @@
         <v>194</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="E14" s="27" t="s">
+        <v>536</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>197</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G14" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>953</v>
+      <c r="I14" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="8" customFormat="1" ht="149.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8344,22 +8631,22 @@
         <v>194</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>538</v>
-      </c>
-      <c r="E15" s="27" t="s">
+        <v>537</v>
+      </c>
+      <c r="E15" s="26" t="s">
         <v>198</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="I15" s="32" t="s">
-        <v>953</v>
+      <c r="I15" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="8" customFormat="1" ht="149.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8371,22 +8658,22 @@
         <v>194</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>539</v>
-      </c>
-      <c r="E16" s="27" t="s">
+        <v>538</v>
+      </c>
+      <c r="E16" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H16" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I16" s="32" t="s">
-        <v>953</v>
+      <c r="I16" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="8" customFormat="1" ht="149.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8398,7 +8685,7 @@
         <v>202</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>203</v>
@@ -8422,7 +8709,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>206</v>
@@ -8446,7 +8733,7 @@
         <v>202</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>209</v>
@@ -8470,7 +8757,7 @@
         <v>202</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>212</v>
@@ -8494,7 +8781,7 @@
         <v>202</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>215</v>
@@ -8518,9 +8805,9 @@
         <v>218</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>545</v>
-      </c>
-      <c r="E22" s="27" t="s">
+        <v>544</v>
+      </c>
+      <c r="E22" s="26" t="s">
         <v>219</v>
       </c>
       <c r="F22" s="9" t="s">
@@ -8532,8 +8819,8 @@
       <c r="H22" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="I22" s="32" t="s">
-        <v>953</v>
+      <c r="I22" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="8" customFormat="1" ht="167.15" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8545,22 +8832,22 @@
         <v>222</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="E23" s="27" t="s">
+        <v>545</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>223</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H23" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="I23" s="32" t="s">
-        <v>953</v>
+      <c r="I23" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8572,22 +8859,22 @@
         <v>225</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>547</v>
-      </c>
-      <c r="E24" s="27" t="s">
+        <v>546</v>
+      </c>
+      <c r="E24" s="26" t="s">
         <v>226</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H24" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="I24" s="32" t="s">
-        <v>953</v>
+      <c r="I24" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8599,22 +8886,22 @@
         <v>229</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>548</v>
-      </c>
-      <c r="E25" s="27" t="s">
+        <v>547</v>
+      </c>
+      <c r="E25" s="26" t="s">
         <v>230</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>173</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H25" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="I25" s="32" t="s">
-        <v>953</v>
+      <c r="I25" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8626,22 +8913,22 @@
         <v>172</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>910</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>902</v>
+        <v>909</v>
+      </c>
+      <c r="E26" s="26" t="s">
+        <v>901</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H26" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I26" s="32" t="s">
-        <v>953</v>
+      <c r="I26" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8653,22 +8940,22 @@
         <v>172</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>911</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>903</v>
+        <v>910</v>
+      </c>
+      <c r="E27" s="26" t="s">
+        <v>902</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="I27" s="32" t="s">
-        <v>953</v>
+      <c r="I27" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8680,22 +8967,22 @@
         <v>176</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="E28" s="27" t="s">
-        <v>904</v>
+        <v>911</v>
+      </c>
+      <c r="E28" s="26" t="s">
+        <v>903</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>953</v>
+        <v>568</v>
+      </c>
+      <c r="I28" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8707,22 +8994,22 @@
         <v>178</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>913</v>
-      </c>
-      <c r="E29" s="27" t="s">
-        <v>905</v>
+        <v>912</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>904</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>953</v>
+        <v>569</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8734,22 +9021,22 @@
         <v>178</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>914</v>
-      </c>
-      <c r="E30" s="27" t="s">
-        <v>906</v>
+        <v>913</v>
+      </c>
+      <c r="E30" s="26" t="s">
+        <v>905</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="I30" s="35" t="s">
-        <v>956</v>
+      <c r="I30" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8761,22 +9048,22 @@
         <v>178</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>915</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>907</v>
+        <v>914</v>
+      </c>
+      <c r="E31" s="26" t="s">
+        <v>906</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H31" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="I31" s="35" t="s">
-        <v>956</v>
+      <c r="I31" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8788,22 +9075,22 @@
         <v>183</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>916</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>908</v>
+        <v>915</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>907</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>185</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="I32" s="35" t="s">
-        <v>956</v>
+        <v>570</v>
+      </c>
+      <c r="I32" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8815,22 +9102,22 @@
         <v>186</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>917</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>909</v>
+        <v>916</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>908</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>572</v>
       </c>
-      <c r="H33" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>956</v>
+      <c r="I33" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8842,22 +9129,22 @@
         <v>194</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>918</v>
-      </c>
-      <c r="E34" s="27" t="s">
-        <v>921</v>
+        <v>917</v>
+      </c>
+      <c r="E34" s="26" t="s">
+        <v>920</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="I34" s="32" t="s">
-        <v>953</v>
+      <c r="I34" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8869,22 +9156,22 @@
         <v>194</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>919</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>922</v>
+        <v>918</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>921</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>580</v>
       </c>
-      <c r="H35" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="I35" s="32" t="s">
-        <v>953</v>
+      <c r="I35" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8896,22 +9183,22 @@
         <v>194</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>920</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>923</v>
+        <v>919</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>922</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H36" s="9" t="s">
         <v>199</v>
       </c>
-      <c r="I36" s="32" t="s">
-        <v>953</v>
+      <c r="I36" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8923,22 +9210,22 @@
         <v>194</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>924</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>929</v>
+        <v>923</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>928</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H37" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="I37" s="32" t="s">
-        <v>953</v>
+      <c r="I37" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8950,13 +9237,13 @@
         <v>218</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>925</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>930</v>
+        <v>924</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>929</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G38" s="9" t="s">
         <v>220</v>
@@ -8964,8 +9251,8 @@
       <c r="H38" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="I38" s="32" t="s">
-        <v>953</v>
+      <c r="I38" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -8977,22 +9264,22 @@
         <v>222</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>926</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>931</v>
+        <v>925</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>930</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H39" s="9" t="s">
         <v>224</v>
       </c>
-      <c r="I39" s="32" t="s">
-        <v>953</v>
+      <c r="I39" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9004,22 +9291,22 @@
         <v>225</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>927</v>
-      </c>
-      <c r="E40" s="27" t="s">
-        <v>932</v>
+        <v>926</v>
+      </c>
+      <c r="E40" s="26" t="s">
+        <v>931</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="I40" s="32" t="s">
-        <v>953</v>
+      <c r="I40" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9031,22 +9318,22 @@
         <v>229</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>928</v>
-      </c>
-      <c r="E41" s="27" t="s">
-        <v>933</v>
+        <v>927</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>932</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="I41" s="32" t="s">
-        <v>953</v>
+      <c r="I41" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="8" customFormat="1" ht="72" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9104,7 +9391,7 @@
     </row>
     <row r="48" spans="1:9" s="8" customFormat="1" ht="22.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -9124,22 +9411,22 @@
         <v>232</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>549</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>555</v>
+        <v>548</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>554</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>227</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H49" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I49" s="34" t="s">
-        <v>953</v>
+      <c r="I49" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="74.150000000000006" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9151,22 +9438,22 @@
         <v>234</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="E50" s="27" t="s">
-        <v>556</v>
+        <v>549</v>
+      </c>
+      <c r="E50" s="26" t="s">
+        <v>555</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>227</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I50" s="34" t="s">
-        <v>953</v>
+      <c r="I50" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="74.150000000000006" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9178,22 +9465,22 @@
         <v>234</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="E51" s="27" t="s">
-        <v>557</v>
+        <v>550</v>
+      </c>
+      <c r="E51" s="26" t="s">
+        <v>556</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>227</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H51" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I51" s="34" t="s">
-        <v>953</v>
+      <c r="I51" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="72.650000000000006" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9205,10 +9492,10 @@
         <v>235</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>227</v>
@@ -9229,10 +9516,10 @@
         <v>238</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>553</v>
-      </c>
-      <c r="E53" s="27" t="s">
-        <v>559</v>
+        <v>552</v>
+      </c>
+      <c r="E53" s="26" t="s">
+        <v>558</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>227</v>
@@ -9243,8 +9530,8 @@
       <c r="H53" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="I53" s="34" t="s">
-        <v>953</v>
+      <c r="I53" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="41.15" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9256,10 +9543,10 @@
         <v>241</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>554</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>560</v>
+        <v>553</v>
+      </c>
+      <c r="E54" s="26" t="s">
+        <v>559</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>227</v>
@@ -9270,8 +9557,8 @@
       <c r="H54" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="I54" s="34" t="s">
-        <v>953</v>
+      <c r="I54" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="55" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -9281,7 +9568,7 @@
     <row r="59" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="1:9" s="8" customFormat="1" ht="22.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -9301,10 +9588,10 @@
         <v>245</v>
       </c>
       <c r="D61" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="E61" s="26" t="s">
         <v>562</v>
-      </c>
-      <c r="E61" s="27" t="s">
-        <v>563</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>227</v>
@@ -9315,8 +9602,8 @@
       <c r="H61" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="I61" s="34" t="s">
-        <v>953</v>
+      <c r="I61" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="42" x14ac:dyDescent="0.25">
@@ -9324,25 +9611,25 @@
         <v>11</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>590</v>
-      </c>
-      <c r="E62" s="27" t="s">
         <v>589</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>588</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>227</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H62" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="I62" s="34" t="s">
-        <v>953</v>
+      <c r="I62" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
   </sheetData>
@@ -9426,7 +9713,7 @@
     </row>
     <row r="4" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -9446,22 +9733,22 @@
         <v>250</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>597</v>
-      </c>
-      <c r="E5" s="30" t="s">
+        <v>596</v>
+      </c>
+      <c r="E5" s="29" t="s">
         <v>251</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>953</v>
+        <v>713</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="28" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -9473,22 +9760,22 @@
         <v>250</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>598</v>
-      </c>
-      <c r="E6" s="30" t="s">
+        <v>597</v>
+      </c>
+      <c r="E6" s="29" t="s">
         <v>253</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>953</v>
+        <v>713</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9500,157 +9787,157 @@
         <v>250</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>599</v>
-      </c>
-      <c r="E7" s="30" t="s">
+        <v>598</v>
+      </c>
+      <c r="E7" s="29" t="s">
         <v>255</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>956</v>
+        <v>591</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>250</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>600</v>
-      </c>
-      <c r="E8" s="30" t="s">
+        <v>599</v>
+      </c>
+      <c r="E8" s="29" t="s">
         <v>257</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>953</v>
+        <v>717</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>250</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="E9" s="30" t="s">
+        <v>600</v>
+      </c>
+      <c r="E9" s="29" t="s">
         <v>258</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G9" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="H9" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>953</v>
+      <c r="I9" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A10" s="7"/>
       <c r="B10" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>250</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>602</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>259</v>
+        <v>601</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>978</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I10" s="32" t="s">
-        <v>953</v>
+        <v>717</v>
+      </c>
+      <c r="I10" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A11" s="7"/>
-      <c r="B11" s="31" t="s">
-        <v>370</v>
+      <c r="B11" s="30" t="s">
+        <v>369</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>250</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>603</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>260</v>
+        <v>602</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>259</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="I11" s="35" t="s">
-        <v>956</v>
+        <v>591</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="A12" s="7"/>
-      <c r="B12" s="31" t="s">
-        <v>370</v>
+      <c r="B12" s="30" t="s">
+        <v>369</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>261</v>
+        <v>603</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>260</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I12" s="32" t="s">
-        <v>953</v>
+        <v>717</v>
+      </c>
+      <c r="I12" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9662,22 +9949,22 @@
         <v>252</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="E13" s="26" t="s">
         <v>724</v>
       </c>
-      <c r="E13" s="27" t="s">
-        <v>725</v>
-      </c>
       <c r="F13" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>594</v>
-      </c>
-      <c r="I13" s="32" t="s">
-        <v>953</v>
+        <v>593</v>
+      </c>
+      <c r="I13" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9689,22 +9976,22 @@
         <v>254</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>725</v>
+      </c>
+      <c r="E14" s="26" t="s">
         <v>726</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>727</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>593</v>
-      </c>
-      <c r="I14" s="32" t="s">
-        <v>953</v>
+        <v>592</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9713,25 +10000,25 @@
         <v>33</v>
       </c>
       <c r="C15" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>728</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>728</v>
-      </c>
-      <c r="E15" s="27" t="s">
-        <v>729</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>953</v>
+      <c r="I15" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9740,25 +10027,25 @@
         <v>33</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>605</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>732</v>
+        <v>604</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>731</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I16" s="32" t="s">
-        <v>953</v>
+        <v>717</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="58.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -9767,805 +10054,805 @@
         <v>33</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>733</v>
+        <v>605</v>
+      </c>
+      <c r="E17" s="26" t="s">
+        <v>732</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="I17" s="32" t="s">
-        <v>953</v>
+        <v>717</v>
+      </c>
+      <c r="I17" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="85.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>336</v>
+        <v>606</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="86" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="E19" s="30" t="s">
-        <v>337</v>
+        <v>607</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>336</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I19" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C20" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G20" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="D20" s="9" t="s">
-        <v>609</v>
-      </c>
-      <c r="E20" s="30" t="s">
-        <v>338</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>312</v>
-      </c>
       <c r="H20" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="E21" s="30" t="s">
-        <v>339</v>
+        <v>609</v>
+      </c>
+      <c r="E21" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I21" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>611</v>
-      </c>
-      <c r="E22" s="30" t="s">
-        <v>340</v>
+        <v>610</v>
+      </c>
+      <c r="E22" s="29" t="s">
+        <v>339</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I22" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="E23" s="30" t="s">
-        <v>341</v>
+        <v>611</v>
+      </c>
+      <c r="E23" s="29" t="s">
+        <v>340</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I23" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>613</v>
-      </c>
-      <c r="E24" s="30" t="s">
-        <v>342</v>
+        <v>612</v>
+      </c>
+      <c r="E24" s="29" t="s">
+        <v>341</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I24" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>614</v>
-      </c>
-      <c r="E25" s="30" t="s">
-        <v>343</v>
+        <v>613</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>342</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I25" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>615</v>
-      </c>
-      <c r="E26" s="30" t="s">
-        <v>344</v>
+        <v>614</v>
+      </c>
+      <c r="E26" s="29" t="s">
+        <v>343</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H26" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I26" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>616</v>
-      </c>
-      <c r="E27" s="30" t="s">
-        <v>345</v>
+        <v>615</v>
+      </c>
+      <c r="E27" s="29" t="s">
+        <v>344</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H27" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I27" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I27" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="E28" s="30" t="s">
-        <v>346</v>
+        <v>616</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>345</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I28" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I28" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>618</v>
-      </c>
-      <c r="E29" s="30" t="s">
-        <v>347</v>
+        <v>617</v>
+      </c>
+      <c r="E29" s="29" t="s">
+        <v>346</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G29" s="23" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H29" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I29" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>619</v>
-      </c>
-      <c r="E30" s="30" t="s">
-        <v>348</v>
+        <v>618</v>
+      </c>
+      <c r="E30" s="29" t="s">
+        <v>347</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I30" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>620</v>
-      </c>
-      <c r="E31" s="30" t="s">
-        <v>349</v>
+        <v>619</v>
+      </c>
+      <c r="E31" s="29" t="s">
+        <v>348</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G31" s="23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H31" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I31" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="E32" s="30" t="s">
-        <v>350</v>
+        <v>620</v>
+      </c>
+      <c r="E32" s="29" t="s">
+        <v>349</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G32" s="23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I32" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I32" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="E33" s="30" t="s">
-        <v>351</v>
+        <v>621</v>
+      </c>
+      <c r="E33" s="29" t="s">
+        <v>350</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G33" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H33" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I33" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I33" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>623</v>
-      </c>
-      <c r="E34" s="30" t="s">
-        <v>352</v>
+        <v>622</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>351</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G34" s="23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I34" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I34" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>624</v>
-      </c>
-      <c r="E35" s="30" t="s">
-        <v>353</v>
+        <v>623</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>352</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I35" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I35" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>625</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>354</v>
+        <v>624</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>353</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G36" s="23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I36" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I36" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>626</v>
-      </c>
-      <c r="E37" s="30" t="s">
-        <v>355</v>
+        <v>625</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>354</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I37" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>627</v>
-      </c>
-      <c r="E38" s="30" t="s">
-        <v>356</v>
+        <v>626</v>
+      </c>
+      <c r="E38" s="29" t="s">
+        <v>355</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G38" s="23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I38" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B39" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>628</v>
-      </c>
-      <c r="E39" s="30" t="s">
-        <v>357</v>
+        <v>627</v>
+      </c>
+      <c r="E39" s="29" t="s">
+        <v>356</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I39" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I39" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="E40" s="30" t="s">
-        <v>358</v>
+        <v>628</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>357</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G40" s="23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I40" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I40" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>630</v>
-      </c>
-      <c r="E41" s="30" t="s">
-        <v>364</v>
+        <v>629</v>
+      </c>
+      <c r="E41" s="29" t="s">
+        <v>363</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I41" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I41" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>631</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>365</v>
+        <v>630</v>
+      </c>
+      <c r="E42" s="29" t="s">
+        <v>364</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I42" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>632</v>
-      </c>
-      <c r="E43" s="30" t="s">
-        <v>366</v>
+        <v>631</v>
+      </c>
+      <c r="E43" s="29" t="s">
+        <v>365</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I43" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I43" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>633</v>
-      </c>
-      <c r="E44" s="30" t="s">
-        <v>367</v>
+        <v>632</v>
+      </c>
+      <c r="E44" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I44" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>634</v>
-      </c>
-      <c r="E45" s="30" t="s">
-        <v>368</v>
+        <v>633</v>
+      </c>
+      <c r="E45" s="29" t="s">
+        <v>367</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I45" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I45" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>635</v>
-      </c>
-      <c r="E46" s="30" t="s">
-        <v>369</v>
+        <v>634</v>
+      </c>
+      <c r="E46" s="29" t="s">
+        <v>368</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I46" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I46" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>635</v>
+      </c>
+      <c r="E47" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G47" s="23" t="s">
         <v>371</v>
       </c>
-      <c r="C47" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>636</v>
-      </c>
-      <c r="E47" s="30" t="s">
-        <v>637</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>372</v>
-      </c>
       <c r="H47" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="I47" s="34" t="s">
-        <v>953</v>
+        <v>309</v>
+      </c>
+      <c r="I47" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="92.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10573,25 +10860,25 @@
         <v>11</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D48" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="E48" s="26" t="s">
         <v>734</v>
       </c>
-      <c r="E48" s="27" t="s">
-        <v>735</v>
-      </c>
       <c r="F48" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G48" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="H48" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="H48" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I48" s="34" t="s">
-        <v>953</v>
+      <c r="I48" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="92.5" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10599,25 +10886,25 @@
         <v>33</v>
       </c>
       <c r="C49" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>735</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="D49" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="E49" s="27" t="s">
-        <v>736</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>295</v>
-      </c>
       <c r="H49" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="I49" s="34" t="s">
-        <v>953</v>
+        <v>291</v>
+      </c>
+      <c r="I49" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="97" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10625,91 +10912,91 @@
         <v>33</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D50" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="E50" s="9" t="s">
-        <v>739</v>
-      </c>
       <c r="F50" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G50" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="H50" s="23" t="s">
         <v>300</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G52" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="H52" s="9" t="s">
         <v>304</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B53" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="H53" s="23" t="s">
         <v>307</v>
-      </c>
-      <c r="H53" s="23" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10717,22 +11004,22 @@
         <v>11</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="H54" s="28" t="s">
-        <v>595</v>
+        <v>286</v>
+      </c>
+      <c r="H54" s="27" t="s">
+        <v>594</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10743,22 +11030,22 @@
         <v>250</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>936</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>939</v>
+        <v>935</v>
+      </c>
+      <c r="E55" s="26" t="s">
+        <v>938</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="I55" s="34" t="s">
-        <v>953</v>
+        <v>713</v>
+      </c>
+      <c r="I55" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="70" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10769,22 +11056,22 @@
         <v>250</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>959</v>
+        <v>936</v>
+      </c>
+      <c r="E56" s="26" t="s">
+        <v>958</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="I56" s="34" t="s">
-        <v>953</v>
+        <v>713</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -10795,28 +11082,28 @@
         <v>250</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>940</v>
+        <v>937</v>
+      </c>
+      <c r="E57" s="26" t="s">
+        <v>939</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>592</v>
-      </c>
-      <c r="I57" s="33" t="s">
-        <v>956</v>
+        <v>591</v>
+      </c>
+      <c r="I57" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="58" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25"/>
     <row r="59" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -10832,25 +11119,25 @@
         <v>11</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D60" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="E60" s="26" t="s">
         <v>638</v>
       </c>
-      <c r="E60" s="27" t="s">
-        <v>639</v>
-      </c>
       <c r="F60" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="I60" s="34" t="s">
-        <v>953</v>
+        <v>284</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="117" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10858,25 +11145,25 @@
         <v>11</v>
       </c>
       <c r="C61" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>639</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>645</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="D61" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="E61" s="27" t="s">
-        <v>646</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="H61" s="23" t="s">
         <v>374</v>
       </c>
-      <c r="H61" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="I61" s="34" t="s">
-        <v>953</v>
+      <c r="I61" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="55" customHeight="1" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10884,25 +11171,25 @@
         <v>11</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>647</v>
+        <v>640</v>
+      </c>
+      <c r="E62" s="26" t="s">
+        <v>646</v>
       </c>
       <c r="F62" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="I62" s="33" t="s">
-        <v>956</v>
+        <v>377</v>
+      </c>
+      <c r="I62" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10910,25 +11197,25 @@
         <v>11</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>642</v>
-      </c>
-      <c r="E63" s="27" t="s">
-        <v>648</v>
+        <v>641</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>647</v>
       </c>
       <c r="F63" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="H63" s="23" t="s">
         <v>377</v>
       </c>
-      <c r="H63" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="I63" s="34" t="s">
-        <v>953</v>
+      <c r="I63" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10936,25 +11223,25 @@
         <v>11</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>643</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>649</v>
+        <v>642</v>
+      </c>
+      <c r="E64" s="26" t="s">
+        <v>648</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="I64" s="34" t="s">
-        <v>953</v>
+        <v>381</v>
+      </c>
+      <c r="I64" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -10962,286 +11249,286 @@
         <v>11</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>644</v>
-      </c>
-      <c r="E65" s="27" t="s">
-        <v>650</v>
+        <v>643</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>649</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H65" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="I65" s="34" t="s">
-        <v>953</v>
+        <v>381</v>
+      </c>
+      <c r="I65" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B66" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C66" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="E66" s="26" t="s">
+        <v>650</v>
+      </c>
+      <c r="F66" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="G66" s="9" t="s">
         <v>380</v>
       </c>
-      <c r="D66" s="9" t="s">
-        <v>645</v>
-      </c>
-      <c r="E66" s="27" t="s">
-        <v>651</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="G66" s="9" t="s">
+      <c r="H66" s="23" t="s">
         <v>381</v>
       </c>
-      <c r="H66" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="I66" s="34" t="s">
-        <v>953</v>
+      <c r="I66" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B67" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D67" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="E67" s="9" t="s">
         <v>749</v>
       </c>
-      <c r="E67" s="9" t="s">
-        <v>750</v>
-      </c>
       <c r="F67" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="H67" s="23" t="s">
         <v>383</v>
-      </c>
-      <c r="H67" s="23" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B68" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G68" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H68" s="23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B69" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C69" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="D69" s="9" t="s">
-        <v>754</v>
-      </c>
       <c r="E69" s="9" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G69" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H69" s="23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B70" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>755</v>
-      </c>
-      <c r="E70" s="27" t="s">
-        <v>762</v>
+        <v>754</v>
+      </c>
+      <c r="E70" s="26" t="s">
+        <v>761</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H70" s="23"/>
-      <c r="I70" s="34" t="s">
-        <v>953</v>
+      <c r="I70" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B71" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="E71" s="27" t="s">
-        <v>763</v>
+        <v>755</v>
+      </c>
+      <c r="E71" s="26" t="s">
+        <v>762</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H71" s="23"/>
-      <c r="I71" s="34" t="s">
-        <v>953</v>
+      <c r="I71" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B72" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>757</v>
-      </c>
-      <c r="E72" s="27" t="s">
-        <v>764</v>
+        <v>756</v>
+      </c>
+      <c r="E72" s="26" t="s">
+        <v>763</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H72" s="23"/>
-      <c r="I72" s="34" t="s">
-        <v>953</v>
+      <c r="I72" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B73" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>758</v>
-      </c>
-      <c r="E73" s="27" t="s">
-        <v>765</v>
+        <v>757</v>
+      </c>
+      <c r="E73" s="26" t="s">
+        <v>764</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H73" s="23"/>
-      <c r="I73" s="34" t="s">
-        <v>953</v>
+      <c r="I73" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B74" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>766</v>
+        <v>758</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>765</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="I74" s="34" t="s">
-        <v>953</v>
+        <v>770</v>
+      </c>
+      <c r="I74" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B75" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C75" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>759</v>
+      </c>
+      <c r="E75" s="26" t="s">
+        <v>766</v>
+      </c>
+      <c r="F75" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G75" s="9" t="s">
         <v>772</v>
       </c>
-      <c r="D75" s="9" t="s">
-        <v>760</v>
-      </c>
-      <c r="E75" s="27" t="s">
-        <v>767</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="I75" s="34" t="s">
-        <v>953</v>
+      <c r="I75" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="42" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B76" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="E76" s="26" t="s">
         <v>785</v>
       </c>
-      <c r="E76" s="27" t="s">
-        <v>786</v>
-      </c>
       <c r="F76" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H76" s="23"/>
-      <c r="I76" s="34" t="s">
-        <v>953</v>
+      <c r="I76" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="77" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
@@ -11259,7 +11546,7 @@
     </row>
     <row r="80" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -11272,103 +11559,103 @@
     </row>
     <row r="81" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B81" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C81" s="24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>652</v>
-      </c>
-      <c r="E81" s="27" t="s">
-        <v>681</v>
+        <v>651</v>
+      </c>
+      <c r="E81" s="26" t="s">
+        <v>680</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G81" s="23" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="I81" s="33" t="s">
-        <v>956</v>
+        <v>386</v>
+      </c>
+      <c r="I81" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B82" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C82" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>652</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>681</v>
+      </c>
+      <c r="F82" s="23" t="s">
         <v>392</v>
       </c>
-      <c r="D82" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>682</v>
-      </c>
-      <c r="F82" s="23" t="s">
-        <v>393</v>
-      </c>
       <c r="G82" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="H82" s="24" t="s">
         <v>390</v>
-      </c>
-      <c r="H82" s="24" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B83" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C83" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>683</v>
+        <v>653</v>
+      </c>
+      <c r="E83" s="26" t="s">
+        <v>682</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>774</v>
       </c>
-      <c r="H83" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="I83" s="34" t="s">
-        <v>953</v>
+      <c r="I83" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B84" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D84" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="E84" s="26" t="s">
         <v>779</v>
       </c>
-      <c r="E84" s="27" t="s">
-        <v>780</v>
-      </c>
       <c r="F84" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G84" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>777</v>
       </c>
-      <c r="H84" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="I84" s="33" t="s">
-        <v>956</v>
+      <c r="I84" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11376,22 +11663,22 @@
         <v>33</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D85" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="E85" s="9" t="s">
+      <c r="F85" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>788</v>
       </c>
-      <c r="F85" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="G85" s="9" t="s">
+      <c r="H85" s="9" t="s">
         <v>789</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="42" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11399,22 +11686,22 @@
         <v>33</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D86" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>781</v>
       </c>
-      <c r="E86" s="9" t="s">
-        <v>782</v>
-      </c>
       <c r="F86" s="23" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="87" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -11422,7 +11709,7 @@
     <row r="89" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25"/>
     <row r="90" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -11435,299 +11722,299 @@
     </row>
     <row r="91" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B91" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C91" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>683</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>794</v>
+      </c>
+      <c r="H91" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="D91" s="9" t="s">
-        <v>655</v>
-      </c>
-      <c r="E91" s="27" t="s">
-        <v>684</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>794</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>795</v>
-      </c>
-      <c r="H91" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="I91" s="34" t="s">
-        <v>953</v>
+      <c r="I91" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B92" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C92" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="E92" s="27" t="s">
-        <v>685</v>
+        <v>655</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>684</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H92" s="9" t="s">
-        <v>793</v>
-      </c>
-      <c r="I92" s="34" t="s">
-        <v>953</v>
+        <v>792</v>
+      </c>
+      <c r="I92" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B93" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C93" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="E93" s="26" t="s">
+        <v>685</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>793</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="H93" s="23" t="s">
         <v>394</v>
       </c>
-      <c r="D93" s="9" t="s">
-        <v>657</v>
-      </c>
-      <c r="E93" s="27" t="s">
-        <v>686</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>794</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>797</v>
-      </c>
-      <c r="H93" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="I93" s="34" t="s">
-        <v>953</v>
+      <c r="I93" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B94" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C94" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="E94" s="27" t="s">
-        <v>687</v>
+        <v>657</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>686</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>793</v>
-      </c>
-      <c r="I94" s="34" t="s">
-        <v>953</v>
+        <v>792</v>
+      </c>
+      <c r="I94" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B95" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D95" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="E95" s="26" t="s">
         <v>801</v>
       </c>
-      <c r="E95" s="27" t="s">
-        <v>802</v>
-      </c>
       <c r="F95" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>798</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>799</v>
       </c>
-      <c r="H95" s="9" t="s">
-        <v>800</v>
-      </c>
-      <c r="I95" s="34" t="s">
-        <v>953</v>
+      <c r="I95" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B96" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>812</v>
-      </c>
-      <c r="E96" s="27" t="s">
-        <v>807</v>
+        <v>811</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>806</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H96" s="9" t="s">
-        <v>805</v>
-      </c>
-      <c r="I96" s="33" t="s">
-        <v>956</v>
+        <v>804</v>
+      </c>
+      <c r="I96" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B97" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C97" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>813</v>
-      </c>
-      <c r="E97" s="27" t="s">
-        <v>808</v>
+        <v>812</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>807</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>806</v>
-      </c>
-      <c r="I97" s="33" t="s">
-        <v>956</v>
+        <v>805</v>
+      </c>
+      <c r="I97" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B98" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C98" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>819</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="F98" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="D98" s="9" t="s">
-        <v>820</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="F98" s="9" t="s">
-        <v>398</v>
-      </c>
       <c r="G98" s="9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B99" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C99" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="F99" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="D99" s="9" t="s">
-        <v>821</v>
-      </c>
-      <c r="E99" s="9" t="s">
-        <v>818</v>
-      </c>
-      <c r="F99" s="9" t="s">
+      <c r="G99" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>398</v>
-      </c>
-      <c r="G99" s="9" t="s">
-        <v>810</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B100" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C100" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>821</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>818</v>
+      </c>
+      <c r="F100" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="D100" s="9" t="s">
-        <v>822</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>819</v>
-      </c>
-      <c r="F100" s="9" t="s">
-        <v>398</v>
-      </c>
       <c r="G100" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="70" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B101" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F101" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="G101" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="G101" s="9" t="s">
-        <v>815</v>
-      </c>
       <c r="H101" s="9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="74" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B102" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F102" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="G102" s="9" t="s">
         <v>814</v>
       </c>
-      <c r="G102" s="9" t="s">
+      <c r="H102" s="9" t="s">
         <v>815</v>
-      </c>
-      <c r="H102" s="9" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="103" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25"/>
@@ -11740,7 +12027,7 @@
     </row>
     <row r="109" spans="1:9" ht="62.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -11753,7 +12040,7 @@
     </row>
     <row r="110" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -11766,158 +12053,158 @@
     </row>
     <row r="111" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B111" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="E111" s="27" t="s">
-        <v>688</v>
+        <v>662</v>
+      </c>
+      <c r="E111" s="26" t="s">
+        <v>687</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="I111" s="33" t="s">
-        <v>956</v>
+        <v>400</v>
+      </c>
+      <c r="I111" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B112" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="E112" s="27" t="s">
-        <v>689</v>
+        <v>663</v>
+      </c>
+      <c r="E112" s="26" t="s">
+        <v>688</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G112" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="H112" s="9" t="s">
         <v>824</v>
       </c>
-      <c r="H112" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="I112" s="33" t="s">
-        <v>956</v>
+      <c r="I112" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B113" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="E113" s="27" t="s">
-        <v>690</v>
+        <v>664</v>
+      </c>
+      <c r="E113" s="26" t="s">
+        <v>689</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="H113" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="I113" s="33" t="s">
-        <v>956</v>
+      <c r="I113" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B114" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>666</v>
-      </c>
-      <c r="E114" s="27" t="s">
-        <v>691</v>
+        <v>665</v>
+      </c>
+      <c r="E114" s="26" t="s">
+        <v>690</v>
       </c>
       <c r="F114" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="H114" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G114" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="H114" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="I114" s="33" t="s">
-        <v>956</v>
+      <c r="I114" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B115" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>829</v>
-      </c>
-      <c r="E115" s="27" t="s">
-        <v>831</v>
+        <v>828</v>
+      </c>
+      <c r="E115" s="26" t="s">
+        <v>830</v>
       </c>
       <c r="F115" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G115" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="I115" s="33" t="s">
-        <v>956</v>
+      <c r="I115" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B116" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>830</v>
-      </c>
-      <c r="E116" s="27" t="s">
-        <v>832</v>
+        <v>829</v>
+      </c>
+      <c r="E116" s="26" t="s">
+        <v>831</v>
       </c>
       <c r="F116" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="H116" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G116" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H116" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="I116" s="33" t="s">
-        <v>956</v>
+      <c r="I116" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="117" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -11971,7 +12258,7 @@
     </row>
     <row r="125" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -11984,360 +12271,360 @@
     </row>
     <row r="126" spans="1:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B126" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="E126" s="27" t="s">
-        <v>659</v>
+        <v>667</v>
+      </c>
+      <c r="E126" s="26" t="s">
+        <v>658</v>
       </c>
       <c r="F126" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H126" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I126" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I126" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B127" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="E127" s="27" t="s">
-        <v>660</v>
+        <v>668</v>
+      </c>
+      <c r="E127" s="26" t="s">
+        <v>659</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I127" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I127" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B128" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>670</v>
-      </c>
-      <c r="E128" s="27" t="s">
-        <v>661</v>
+        <v>669</v>
+      </c>
+      <c r="E128" s="26" t="s">
+        <v>660</v>
       </c>
       <c r="F128" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H128" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I128" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I128" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="129" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B129" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="E129" s="27" t="s">
-        <v>662</v>
+        <v>670</v>
+      </c>
+      <c r="E129" s="26" t="s">
+        <v>661</v>
       </c>
       <c r="F129" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I129" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I129" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="130" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B130" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>834</v>
-      </c>
-      <c r="E130" s="27" t="s">
-        <v>836</v>
+        <v>833</v>
+      </c>
+      <c r="E130" s="26" t="s">
+        <v>835</v>
       </c>
       <c r="F130" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H130" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I130" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I130" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="131" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B131" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>835</v>
-      </c>
-      <c r="E131" s="27" t="s">
-        <v>837</v>
+        <v>834</v>
+      </c>
+      <c r="E131" s="26" t="s">
+        <v>836</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I131" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I131" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="132" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B132" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>846</v>
-      </c>
-      <c r="E132" s="27" t="s">
-        <v>851</v>
+        <v>845</v>
+      </c>
+      <c r="E132" s="26" t="s">
+        <v>850</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H132" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I132" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I132" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="133" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B133" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>847</v>
-      </c>
-      <c r="E133" s="27" t="s">
-        <v>852</v>
+        <v>846</v>
+      </c>
+      <c r="E133" s="26" t="s">
+        <v>851</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I133" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I133" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="134" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B134" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>848</v>
-      </c>
-      <c r="E134" s="27" t="s">
-        <v>853</v>
+        <v>847</v>
+      </c>
+      <c r="E134" s="26" t="s">
+        <v>852</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H134" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I134" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I134" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="135" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B135" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>849</v>
-      </c>
-      <c r="E135" s="27" t="s">
-        <v>854</v>
+        <v>848</v>
+      </c>
+      <c r="E135" s="26" t="s">
+        <v>853</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I135" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I135" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="136" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B136" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>850</v>
-      </c>
-      <c r="E136" s="27" t="s">
-        <v>855</v>
+        <v>849</v>
+      </c>
+      <c r="E136" s="26" t="s">
+        <v>854</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H136" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="I136" s="33" t="s">
-        <v>956</v>
+        <v>403</v>
+      </c>
+      <c r="I136" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="137" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B137" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D137" s="9" t="s">
+        <v>859</v>
+      </c>
+      <c r="E137" s="26" t="s">
         <v>860</v>
       </c>
-      <c r="E137" s="27" t="s">
-        <v>861</v>
-      </c>
       <c r="F137" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="I137" s="33" t="s">
-        <v>956</v>
+        <v>406</v>
+      </c>
+      <c r="I137" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="138" spans="2:9" ht="70" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B138" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H138" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="139" spans="2:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B139" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>244</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G139" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="H139" s="9" t="s">
         <v>409</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="140" spans="2:9" outlineLevel="3" x14ac:dyDescent="0.25"/>
@@ -12352,7 +12639,7 @@
     </row>
     <row r="146" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B146" s="5"/>
       <c r="C146" s="5"/>
@@ -12366,210 +12653,210 @@
     <row r="147" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="A147" s="9"/>
       <c r="B147" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C147" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="D147" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="D147" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="E147" s="27" t="s">
-        <v>692</v>
+      <c r="E147" s="26" t="s">
+        <v>691</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G147" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="H147" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="H147" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="I147" s="32" t="s">
-        <v>953</v>
+      <c r="I147" s="31" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B148" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="E148" s="27" t="s">
-        <v>693</v>
+        <v>677</v>
+      </c>
+      <c r="E148" s="26" t="s">
+        <v>692</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G148" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H148" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="H148" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="I148" s="33" t="s">
-        <v>956</v>
+      <c r="I148" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B149" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="E149" s="27" t="s">
-        <v>694</v>
+        <v>678</v>
+      </c>
+      <c r="E149" s="26" t="s">
+        <v>693</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G149" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="H149" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="H149" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="I149" s="33" t="s">
-        <v>956</v>
+      <c r="I149" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B150" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>871</v>
-      </c>
-      <c r="E150" s="27" t="s">
         <v>870</v>
       </c>
+      <c r="E150" s="26" t="s">
+        <v>869</v>
+      </c>
       <c r="F150" s="9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G150" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H150" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="H150" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="I150" s="33" t="s">
-        <v>956</v>
+      <c r="I150" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B151" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>872</v>
-      </c>
-      <c r="E151" s="27" t="s">
-        <v>876</v>
+        <v>871</v>
+      </c>
+      <c r="E151" s="26" t="s">
+        <v>875</v>
       </c>
       <c r="F151" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="G151" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="G151" s="9" t="s">
+      <c r="H151" s="9" t="s">
         <v>868</v>
       </c>
-      <c r="H151" s="9" t="s">
-        <v>869</v>
-      </c>
-      <c r="I151" s="34" t="s">
-        <v>953</v>
+      <c r="I151" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B152" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>873</v>
-      </c>
-      <c r="E152" s="27" t="s">
-        <v>877</v>
+        <v>872</v>
+      </c>
+      <c r="E152" s="26" t="s">
+        <v>876</v>
       </c>
       <c r="F152" s="9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G152" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="H152" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="H152" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="I152" s="33" t="s">
-        <v>956</v>
+      <c r="I152" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B153" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="E153" s="27" t="s">
-        <v>878</v>
+        <v>873</v>
+      </c>
+      <c r="E153" s="26" t="s">
+        <v>877</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G153" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="H153" s="9" t="s">
         <v>415</v>
       </c>
-      <c r="H153" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="I153" s="33" t="s">
-        <v>956</v>
+      <c r="I153" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="56" outlineLevel="3" x14ac:dyDescent="0.25">
       <c r="B154" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>875</v>
-      </c>
-      <c r="E154" s="27" t="s">
-        <v>879</v>
+        <v>874</v>
+      </c>
+      <c r="E154" s="26" t="s">
+        <v>878</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G154" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H154" s="9" t="s">
         <v>417</v>
       </c>
-      <c r="H154" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="I154" s="33" t="s">
-        <v>956</v>
+      <c r="I154" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="155" spans="1:9" outlineLevel="3" x14ac:dyDescent="0.25">
@@ -12640,7 +12927,7 @@
     </row>
     <row r="165" spans="1:9" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -12654,80 +12941,80 @@
     <row r="166" spans="1:9" ht="65" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A166" s="9"/>
       <c r="B166" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C166" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="E166" s="26" t="s">
+        <v>696</v>
+      </c>
+      <c r="F166" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>882</v>
+      </c>
+      <c r="H166" s="9" t="s">
         <v>889</v>
       </c>
-      <c r="D166" s="9" t="s">
-        <v>695</v>
-      </c>
-      <c r="E166" s="27" t="s">
-        <v>697</v>
-      </c>
-      <c r="F166" s="9" t="s">
-        <v>881</v>
-      </c>
-      <c r="G166" s="9" t="s">
-        <v>883</v>
-      </c>
-      <c r="H166" s="9" t="s">
-        <v>890</v>
-      </c>
-      <c r="I166" s="35" t="s">
-        <v>956</v>
+      <c r="I166" s="34" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B167" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C167" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D167" s="9" t="s">
-        <v>696</v>
-      </c>
-      <c r="E167" s="27" t="s">
-        <v>698</v>
+        <v>695</v>
+      </c>
+      <c r="E167" s="26" t="s">
+        <v>697</v>
       </c>
       <c r="F167" s="9" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="G167" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H167" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="H167" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="I167" s="33" t="s">
-        <v>956</v>
+      <c r="I167" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="84.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B168" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D168" s="9" t="s">
-        <v>892</v>
-      </c>
-      <c r="E168" s="27" t="s">
+        <v>891</v>
+      </c>
+      <c r="E168" s="26" t="s">
+        <v>879</v>
+      </c>
+      <c r="F168" s="9" t="s">
         <v>880</v>
       </c>
-      <c r="F168" s="9" t="s">
-        <v>881</v>
-      </c>
       <c r="G168" s="9" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H168" s="9" t="s">
-        <v>890</v>
-      </c>
-      <c r="I168" s="33" t="s">
-        <v>956</v>
+        <v>889</v>
+      </c>
+      <c r="I168" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="169" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25"/>
@@ -12746,7 +13033,7 @@
     </row>
     <row r="173" spans="1:9" ht="28" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -12759,7 +13046,7 @@
     </row>
     <row r="174" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -12772,106 +13059,106 @@
     </row>
     <row r="175" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B175" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>894</v>
-      </c>
-      <c r="E175" s="27" t="s">
-        <v>699</v>
+        <v>893</v>
+      </c>
+      <c r="E175" s="26" t="s">
+        <v>698</v>
       </c>
       <c r="F175" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="G175" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="G175" s="9" t="s">
+      <c r="H175" s="9" t="s">
         <v>425</v>
       </c>
-      <c r="H175" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="I175" s="33" t="s">
-        <v>956</v>
+      <c r="I175" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B176" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D176" s="9" t="s">
-        <v>895</v>
-      </c>
-      <c r="E176" s="27" t="s">
-        <v>700</v>
+        <v>894</v>
+      </c>
+      <c r="E176" s="26" t="s">
+        <v>699</v>
       </c>
       <c r="F176" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G176" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H176" s="9" t="s">
         <v>427</v>
       </c>
-      <c r="H176" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="I176" s="34" t="s">
-        <v>953</v>
+      <c r="I176" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B177" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D177" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E177" s="26" t="s">
         <v>896</v>
       </c>
-      <c r="E177" s="27" t="s">
-        <v>897</v>
-      </c>
       <c r="F177" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="I177" s="33" t="s">
-        <v>956</v>
+        <v>427</v>
+      </c>
+      <c r="I177" s="32" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B178" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D178" s="9" t="s">
+        <v>897</v>
+      </c>
+      <c r="E178" s="26" t="s">
+        <v>900</v>
+      </c>
+      <c r="F178" s="9" t="s">
         <v>898</v>
       </c>
-      <c r="E178" s="27" t="s">
-        <v>901</v>
-      </c>
-      <c r="F178" s="9" t="s">
+      <c r="G178" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="H178" s="9" t="s">
         <v>899</v>
       </c>
-      <c r="G178" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="H178" s="9" t="s">
-        <v>900</v>
-      </c>
-      <c r="I178" s="34" t="s">
-        <v>953</v>
+      <c r="I178" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="179" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25"/>
@@ -12883,7 +13170,7 @@
     </row>
     <row r="182" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -12896,94 +13183,94 @@
     </row>
     <row r="183" spans="1:9" ht="70" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B183" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D183" s="9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="F183" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G183" s="9" t="s">
         <v>429</v>
       </c>
-      <c r="G183" s="9" t="s">
-        <v>430</v>
-      </c>
       <c r="H183" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="70" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B184" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D184" s="9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E184" s="9" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="F184" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G184" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H184" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="70" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B185" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C185" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="F185" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B186" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C186" s="9" t="s">
         <v>244</v>
       </c>
       <c r="D186" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E186" s="9" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="F186" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G186" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H186" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="187" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25"/>
@@ -12992,7 +13279,7 @@
     </row>
     <row r="189" spans="1:9" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -13005,77 +13292,77 @@
     </row>
     <row r="190" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B190" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C190" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D190" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="E190" s="27" t="s">
-        <v>708</v>
+        <v>704</v>
+      </c>
+      <c r="E190" s="26" t="s">
+        <v>707</v>
       </c>
       <c r="F190" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G190" s="9" t="s">
+        <v>433</v>
+      </c>
+      <c r="H190" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="H190" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="I190" s="34" t="s">
-        <v>953</v>
+      <c r="I190" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B191" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C191" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="D191" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="E191" s="26" t="s">
+        <v>708</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="G191" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="D191" s="9" t="s">
-        <v>706</v>
-      </c>
-      <c r="E191" s="27" t="s">
-        <v>709</v>
-      </c>
-      <c r="F191" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="G191" s="9" t="s">
-        <v>437</v>
-      </c>
       <c r="H191" s="9" t="s">
-        <v>958</v>
-      </c>
-      <c r="I191" s="34" t="s">
-        <v>953</v>
+        <v>957</v>
+      </c>
+      <c r="I191" s="33" t="s">
+        <v>952</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="56" outlineLevel="2" x14ac:dyDescent="0.25">
       <c r="B192" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C192" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D192" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E192" s="9" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="F192" s="9" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G192" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H192" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:9" outlineLevel="2" x14ac:dyDescent="0.25">
@@ -13110,8 +13397,8 @@
       <c r="C197" s="9"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="29" t="s">
-        <v>281</v>
+      <c r="A198" s="28" t="s">
+        <v>280</v>
       </c>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -13124,48 +13411,48 @@
     </row>
     <row r="199" spans="1:9" ht="42" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B199" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C199" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D199" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F199" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="G199" s="9" t="s">
         <v>441</v>
       </c>
-      <c r="G199" s="9" t="s">
+      <c r="H199" s="9" t="s">
         <v>442</v>
-      </c>
-      <c r="H199" s="9" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="42" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B200" s="11" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C200" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D200" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="E200" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="E200" s="9" t="s">
-        <v>713</v>
-      </c>
       <c r="F200" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G200" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="H200" s="9" t="s">
         <v>444</v>
-      </c>
-      <c r="H200" s="9" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -13189,35 +13476,169 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9075756-EA39-43EB-AFDD-B8F75EBD8DC2}">
-  <dimension ref="A6:G8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.90625" customWidth="1"/>
+    <col min="2" max="2" width="9.6328125" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" customWidth="1"/>
+    <col min="5" max="5" width="19.81640625" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="28.36328125" customWidth="1"/>
+    <col min="8" max="8" width="23.7265625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="102.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D2" s="44" t="s">
+        <v>960</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>979</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>974</v>
+      </c>
+      <c r="G2" s="45" t="s">
+        <v>970</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>961</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="75.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D3" s="44" t="s">
+        <v>962</v>
+      </c>
+      <c r="E3" s="46" t="s">
+        <v>980</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>974</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>971</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>963</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="71" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D4" s="44" t="s">
+        <v>964</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>981</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>975</v>
+      </c>
+      <c r="G4" s="45" t="s">
+        <v>971</v>
+      </c>
+      <c r="H4" s="22" t="s">
+        <v>965</v>
+      </c>
+      <c r="I4" s="33" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="44"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:9" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D6" s="44" t="s">
+        <v>966</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>982</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>976</v>
+      </c>
+      <c r="G6" s="45" t="s">
+        <v>972</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>967</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="42"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="47"/>
+      <c r="G7" s="47"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="58" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D8" s="44" t="s">
+        <v>968</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>983</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>977</v>
+      </c>
+      <c r="G8" s="45" t="s">
+        <v>973</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>969</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="E9" s="46"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>984</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
